--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$86</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3290" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3328" uniqueCount="640">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T10:00:28+00:00</t>
+    <t>2025-07-07T12:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -665,6 +665,22 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -2319,7 +2335,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP85"/>
+  <dimension ref="A1:AP86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.46484375" customWidth="true" bestFit="true"/>
@@ -4650,43 +4666,41 @@
         <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>114</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4734,7 +4748,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4743,7 +4757,7 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>122</v>
@@ -4758,7 +4772,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4776,7 +4790,7 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4789,23 +4803,25 @@
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4854,7 +4870,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4866,22 +4882,22 @@
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4889,14 +4905,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4915,17 +4931,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4974,7 +4990,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4989,19 +5005,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -5009,14 +5025,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5035,18 +5051,18 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5094,7 +5110,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5109,16 +5125,16 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5129,46 +5145,44 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>244</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5192,11 +5206,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5214,13 +5230,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -5229,19 +5245,19 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5249,10 +5265,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5263,31 +5279,31 @@
         <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>169</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5312,35 +5328,35 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -5349,19 +5365,19 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5369,14 +5385,12 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5385,7 +5399,7 @@
         <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>94</v>
@@ -5397,19 +5411,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5437,28 +5451,26 @@
         <v>173</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5482,10 +5494,10 @@
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5493,24 +5505,26 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -5519,16 +5533,20 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>107</v>
+        <v>258</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>108</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5552,13 +5570,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5576,19 +5594,19 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>110</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5600,10 +5618,10 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>111</v>
+        <v>266</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5611,21 +5629,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5637,17 +5655,15 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5684,31 +5700,31 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5731,46 +5747,44 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>115</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>272</v>
+        <v>116</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5806,19 +5820,19 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>121</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5830,7 +5844,7 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5839,10 +5853,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>277</v>
+        <v>111</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5853,10 +5867,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5864,31 +5878,35 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>108</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5936,19 +5954,19 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -5957,10 +5975,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>111</v>
+        <v>282</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5971,21 +5989,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5997,17 +6015,15 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -6044,31 +6060,31 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6091,52 +6107,50 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>284</v>
+        <v>115</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>285</v>
+        <v>116</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>82</v>
@@ -6166,31 +6180,31 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>289</v>
+        <v>121</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6199,10 +6213,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>291</v>
+        <v>111</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6213,10 +6227,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6224,13 +6238,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
@@ -6239,24 +6253,26 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>82</v>
@@ -6298,7 +6314,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6319,10 +6335,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6333,10 +6349,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6344,13 +6360,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -6359,24 +6375,24 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6418,7 +6434,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6439,10 +6455,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6453,10 +6469,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6464,13 +6480,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6479,24 +6495,24 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6538,7 +6554,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6559,10 +6575,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6573,10 +6589,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6599,19 +6615,17 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>319</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6660,7 +6674,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6681,10 +6695,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6695,10 +6709,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6721,19 +6735,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>324</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6782,7 +6796,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6803,10 +6817,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6817,24 +6831,24 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6843,19 +6857,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6880,13 +6894,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6904,10 +6918,10 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>93</v>
@@ -6919,62 +6933,66 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>258</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>108</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6998,13 +7016,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7022,10 +7040,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>110</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>93</v>
@@ -7034,44 +7052,44 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>111</v>
+        <v>352</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7083,17 +7101,15 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7130,31 +7146,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7177,18 +7193,18 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>81</v>
@@ -7200,23 +7216,21 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>271</v>
+        <v>115</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>272</v>
+        <v>116</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7252,9 +7266,11 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7262,7 +7278,7 @@
         <v>120</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>275</v>
+        <v>121</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7274,7 +7290,7 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7283,10 +7299,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>277</v>
+        <v>111</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7297,14 +7313,12 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7313,7 +7327,7 @@
         <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7328,16 +7342,16 @@
         <v>147</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7347,7 +7361,7 @@
         <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7374,19 +7388,17 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7407,10 +7419,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7421,18 +7433,20 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="C43" s="2"/>
+      <c r="C43" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -7447,19 +7461,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>329</v>
+        <v>276</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>331</v>
+        <v>278</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>332</v>
+        <v>279</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7469,7 +7483,7 @@
         <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>82</v>
@@ -7508,13 +7522,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7529,10 +7543,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>334</v>
+        <v>281</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7543,10 +7557,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7554,13 +7568,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
@@ -7569,19 +7583,19 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>359</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7630,7 +7644,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7645,19 +7659,19 @@
         <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7665,10 +7679,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7676,13 +7690,13 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7691,18 +7705,20 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7750,13 +7766,13 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
@@ -7765,19 +7781,19 @@
         <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7785,21 +7801,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7811,20 +7827,18 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>380</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7872,13 +7886,13 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
@@ -7887,19 +7901,19 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7907,24 +7921,24 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
@@ -7933,19 +7947,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7994,7 +8008,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8003,25 +8017,25 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>393</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -8029,24 +8043,24 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
@@ -8055,18 +8069,20 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>129</v>
+        <v>392</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8114,7 +8130,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8123,25 +8139,25 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>398</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8149,10 +8165,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8163,7 +8179,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8175,18 +8191,18 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L49" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>409</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8234,13 +8250,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -8249,19 +8265,19 @@
         <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8269,10 +8285,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8283,10 +8299,10 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -8295,19 +8311,17 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8344,55 +8358,57 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8406,25 +8422,29 @@
         <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>420</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>108</v>
+        <v>421</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8460,19 +8480,17 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>110</v>
+        <v>419</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8481,47 +8499,47 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>111</v>
+        <v>428</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8533,17 +8551,15 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8580,31 +8596,31 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8627,21 +8643,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8650,23 +8666,21 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>428</v>
+        <v>114</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>429</v>
+        <v>115</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>430</v>
+        <v>116</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8702,31 +8716,31 @@
         <v>82</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>433</v>
+        <v>121</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8735,10 +8749,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>435</v>
+        <v>111</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8749,10 +8763,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8760,7 +8774,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>93</v>
@@ -8769,74 +8783,74 @@
         <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>169</v>
+        <v>433</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="P54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="P54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q54" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="R54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8857,10 +8871,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8871,10 +8885,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8891,33 +8905,35 @@
         <v>82</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q55" s="2"/>
+      <c r="Q55" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="R55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>82</v>
@@ -8932,13 +8948,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>82</v>
+        <v>447</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8956,7 +8972,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8977,10 +8993,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8991,10 +9007,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9017,17 +9033,17 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9037,7 +9053,7 @@
         <v>82</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>82</v>
@@ -9076,7 +9092,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9085,7 +9101,7 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>460</v>
+        <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
@@ -9097,10 +9113,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9111,10 +9127,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9122,7 +9138,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>93</v>
@@ -9137,19 +9153,17 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9159,7 +9173,7 @@
         <v>82</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>82</v>
@@ -9198,7 +9212,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9207,7 +9221,7 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>82</v>
+        <v>465</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>105</v>
@@ -9219,10 +9233,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9233,10 +9247,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9244,34 +9258,34 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J58" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K58" t="s" s="2">
-        <v>253</v>
+        <v>169</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9296,13 +9310,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>475</v>
+        <v>82</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9320,7 +9334,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9329,7 +9343,7 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -9341,10 +9355,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>192</v>
+        <v>457</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9355,24 +9369,24 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
@@ -9381,19 +9395,19 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9421,10 +9435,10 @@
         <v>151</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9442,16 +9456,16 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9460,31 +9474,31 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>487</v>
+        <v>192</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9503,19 +9517,19 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>491</v>
+        <v>258</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9540,13 +9554,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>82</v>
+        <v>489</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9564,7 +9578,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9582,27 +9596,27 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9613,7 +9627,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9625,18 +9639,20 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>253</v>
+        <v>496</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="N61" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9660,13 +9676,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9684,13 +9700,13 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
@@ -9702,27 +9718,27 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>507</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9745,20 +9761,18 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9785,10 +9799,10 @@
         <v>159</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9806,7 +9820,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9824,27 +9838,27 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>82</v>
+        <v>512</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9867,18 +9881,20 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>518</v>
+        <v>258</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9902,13 +9918,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>518</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9926,7 +9942,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9944,27 +9960,27 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9978,7 +9994,7 @@
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>82</v>
@@ -9987,16 +10003,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10046,7 +10062,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10064,27 +10080,27 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10095,10 +10111,10 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
@@ -10107,20 +10123,18 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>540</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10168,45 +10182,45 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>541</v>
+        <v>105</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10217,7 +10231,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -10229,16 +10243,20 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>541</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>108</v>
+        <v>542</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10286,19 +10304,19 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -10307,10 +10325,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>111</v>
+        <v>548</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10321,21 +10339,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10347,17 +10365,15 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10406,19 +10422,19 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10441,14 +10457,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>547</v>
+        <v>113</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10461,26 +10477,24 @@
         <v>82</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>548</v>
+        <v>115</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>549</v>
+        <v>116</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O68" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10528,7 +10542,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>550</v>
+        <v>121</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10552,7 +10566,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10570,26 +10584,26 @@
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>82</v>
+        <v>552</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>552</v>
+        <v>114</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>553</v>
@@ -10597,8 +10611,12 @@
       <c r="M69" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+      <c r="N69" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10646,19 +10664,19 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10667,10 +10685,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>557</v>
+        <v>192</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10681,10 +10699,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10707,13 +10725,13 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10764,7 +10782,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10773,7 +10791,7 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
@@ -10785,10 +10803,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10799,10 +10817,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10825,20 +10843,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>253</v>
+        <v>557</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N71" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="O71" t="s" s="2">
-        <v>566</v>
-      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10862,13 +10876,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>173</v>
+        <v>82</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>567</v>
+        <v>82</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>568</v>
+        <v>82</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10886,7 +10900,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10895,7 +10909,7 @@
         <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>82</v>
+        <v>560</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>105</v>
@@ -10904,13 +10918,13 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>569</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>488</v>
+        <v>566</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10921,10 +10935,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10935,7 +10949,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10947,19 +10961,19 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10984,13 +10998,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11008,13 +11022,13 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
@@ -11026,13 +11040,13 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11043,10 +11057,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11057,7 +11071,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -11069,17 +11083,19 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11104,13 +11120,13 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>82</v>
+        <v>581</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>82</v>
+        <v>582</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11128,13 +11144,13 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
@@ -11146,13 +11162,13 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>82</v>
+        <v>574</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>82</v>
+        <v>575</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>583</v>
+        <v>493</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11163,10 +11179,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11189,7 +11205,7 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>107</v>
+        <v>584</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>585</v>
@@ -11198,7 +11214,9 @@
         <v>586</v>
       </c>
       <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>587</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11246,7 +11264,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11267,10 +11285,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11281,10 +11299,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11295,7 +11313,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11304,10 +11322,10 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>589</v>
+        <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>590</v>
@@ -11315,9 +11333,7 @@
       <c r="M75" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="N75" t="s" s="2">
-        <v>592</v>
-      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11366,13 +11382,13 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
@@ -11387,10 +11403,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>593</v>
+        <v>561</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11401,10 +11417,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11427,16 +11443,16 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11486,7 +11502,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11507,10 +11523,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11521,10 +11537,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11538,7 +11554,7 @@
         <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>82</v>
@@ -11547,20 +11563,18 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>536</v>
+        <v>601</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>602</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="O77" t="s" s="2">
         <v>604</v>
       </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11608,7 +11622,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11620,19 +11634,19 @@
         <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11643,10 +11657,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11657,28 +11671,32 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>107</v>
+        <v>541</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>108</v>
+        <v>607</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11726,19 +11744,19 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>110</v>
+        <v>606</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11747,10 +11765,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>111</v>
+        <v>612</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11761,21 +11779,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11787,17 +11805,15 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11846,19 +11862,19 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11881,14 +11897,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>547</v>
+        <v>113</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11901,26 +11917,24 @@
         <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>548</v>
+        <v>115</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>549</v>
+        <v>116</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O80" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -11968,7 +11982,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>550</v>
+        <v>121</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11992,7 +12006,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12003,45 +12017,45 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>82</v>
+        <v>552</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I81" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>253</v>
+        <v>114</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>612</v>
+        <v>553</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>613</v>
+        <v>554</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>614</v>
+        <v>117</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>615</v>
+        <v>216</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12066,13 +12080,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12090,34 +12104,34 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>611</v>
+        <v>555</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>347</v>
+        <v>192</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>82</v>
@@ -12125,10 +12139,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12136,7 +12150,7 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>93</v>
@@ -12151,19 +12165,19 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12191,10 +12205,10 @@
         <v>151</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>622</v>
+        <v>347</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>623</v>
+        <v>348</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12212,16 +12226,16 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>624</v>
+        <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>105</v>
@@ -12230,27 +12244,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>422</v>
+        <v>351</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>423</v>
+        <v>352</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12270,22 +12284,22 @@
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>253</v>
+        <v>623</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>473</v>
+        <v>423</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12313,10 +12327,10 @@
         <v>151</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>474</v>
+        <v>627</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>475</v>
+        <v>628</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12334,7 +12348,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12343,7 +12357,7 @@
         <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>105</v>
@@ -12352,19 +12366,19 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>82</v>
+        <v>630</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>192</v>
+        <v>427</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>477</v>
+        <v>428</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
     </row>
     <row r="84" hidden="true">
@@ -12376,17 +12390,17 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12395,19 +12409,19 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>480</v>
+        <v>632</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>481</v>
+        <v>633</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>482</v>
+        <v>634</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12435,10 +12449,10 @@
         <v>151</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12462,10 +12476,10 @@
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>82</v>
+        <v>635</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>105</v>
@@ -12474,31 +12488,31 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>487</v>
+        <v>192</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12517,19 +12531,19 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>83</v>
+        <v>258</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>633</v>
+        <v>485</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>634</v>
+        <v>486</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>539</v>
+        <v>487</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>540</v>
+        <v>488</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12554,13 +12568,13 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>82</v>
+        <v>489</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
@@ -12578,7 +12592,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12596,23 +12610,145 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>542</v>
+        <v>492</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>543</v>
+        <v>493</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP86" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP85">
+  <autoFilter ref="A1:AP86">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12622,7 +12758,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
+  <conditionalFormatting sqref="A2:AI85">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T12:38:35+00:00</t>
+    <t>2025-07-07T15:58:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1299,7 +1299,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2348,7 +2348,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="191.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="179.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:58:33+00:00</t>
+    <t>2025-07-07T16:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
